--- a/AAII_Financials/Yearly/V_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/V_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Yearly/V_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/V_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
   <si>
     <t>V</t>
   </si>
@@ -656,212 +656,224 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="7" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44834</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44469</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44104</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43738</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43373</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43008</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42643</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42277</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41912</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41547</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41182</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40816</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>35926000</v>
+      </c>
+      <c r="E8" s="3">
         <v>32653000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>29310000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>24105000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>21846000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>22977000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>20609000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>18358000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>15082000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>13880000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>12702000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>11778000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>10421000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>9188000</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>6567000</v>
+        <v>778000</v>
       </c>
       <c r="E9" s="3">
-        <v>5708000</v>
+        <v>736000</v>
       </c>
       <c r="F9" s="3">
-        <v>4970000</v>
+        <v>743000</v>
       </c>
       <c r="G9" s="3">
-        <v>4512000</v>
+        <v>730000</v>
       </c>
       <c r="H9" s="3">
-        <v>4165000</v>
+        <v>727000</v>
       </c>
       <c r="I9" s="3">
-        <v>3856000</v>
+        <v>721000</v>
       </c>
       <c r="J9" s="3">
+        <v>686000</v>
+      </c>
+      <c r="K9" s="3">
         <v>3248000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2764000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2553000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2382000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1932000</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="P9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>26086000</v>
+        <v>35148000</v>
       </c>
       <c r="E10" s="3">
-        <v>23602000</v>
+        <v>31917000</v>
       </c>
       <c r="F10" s="3">
-        <v>19135000</v>
+        <v>28567000</v>
       </c>
       <c r="G10" s="3">
-        <v>17334000</v>
+        <v>23375000</v>
       </c>
       <c r="H10" s="3">
-        <v>18812000</v>
+        <v>21119000</v>
       </c>
       <c r="I10" s="3">
-        <v>16753000</v>
+        <v>22256000</v>
       </c>
       <c r="J10" s="3">
+        <v>19923000</v>
+      </c>
+      <c r="K10" s="3">
         <v>15110000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>12318000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>11327000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>10320000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>9846000</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="P10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -879,8 +891,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -923,9 +936,12 @@
       <c r="P12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -968,99 +984,108 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>927000</v>
+        <v>388000</v>
       </c>
       <c r="E14" s="3">
-        <v>928000</v>
+        <v>1009000</v>
       </c>
       <c r="F14" s="3">
-        <v>3000</v>
+        <v>1164000</v>
       </c>
       <c r="G14" s="3">
-        <v>11000</v>
+        <v>-744000</v>
       </c>
       <c r="H14" s="3">
-        <v>400000</v>
+        <v>-109000</v>
       </c>
       <c r="I14" s="3">
-        <v>607000</v>
+        <v>264000</v>
       </c>
       <c r="J14" s="3">
+        <v>310000</v>
+      </c>
+      <c r="K14" s="3">
         <v>19000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1879000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>14000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>453000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>18000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>4106000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>7000</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1034000</v>
+      </c>
+      <c r="E15" s="3">
         <v>943000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>861000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>804000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>767000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>656000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>613000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>556000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>502000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>494000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>435000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>397000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>333000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>288000</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1075,98 +1100,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>11653000</v>
+        <v>11987000</v>
       </c>
       <c r="E17" s="3">
-        <v>10497000</v>
+        <v>10726000</v>
       </c>
       <c r="F17" s="3">
-        <v>8301000</v>
+        <v>9629000</v>
       </c>
       <c r="G17" s="3">
-        <v>7765000</v>
+        <v>8298000</v>
       </c>
       <c r="H17" s="3">
-        <v>7976000</v>
+        <v>7721000</v>
       </c>
       <c r="I17" s="3">
-        <v>7655000</v>
+        <v>7539000</v>
       </c>
       <c r="J17" s="3">
+        <v>7005000</v>
+      </c>
+      <c r="K17" s="3">
         <v>6214000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7199000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4816000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5005000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4554000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>8288000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3732000</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>21000000</v>
+        <v>23939000</v>
       </c>
       <c r="E18" s="3">
-        <v>18813000</v>
+        <v>21927000</v>
       </c>
       <c r="F18" s="3">
-        <v>15804000</v>
+        <v>19681000</v>
       </c>
       <c r="G18" s="3">
-        <v>14081000</v>
+        <v>15807000</v>
       </c>
       <c r="H18" s="3">
-        <v>15001000</v>
+        <v>14125000</v>
       </c>
       <c r="I18" s="3">
-        <v>12954000</v>
+        <v>15438000</v>
       </c>
       <c r="J18" s="3">
+        <v>13604000</v>
+      </c>
+      <c r="K18" s="3">
         <v>12144000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>7883000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>9064000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>7697000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>7224000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2133000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>5456000</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1184,127 +1216,134 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>681000</v>
+        <v>-14000</v>
       </c>
       <c r="E20" s="3">
-        <v>-139000</v>
+        <v>-18000</v>
       </c>
       <c r="F20" s="3">
-        <v>772000</v>
+        <v>-88000</v>
       </c>
       <c r="G20" s="3">
-        <v>225000</v>
+        <v>-25000</v>
       </c>
       <c r="H20" s="3">
-        <v>416000</v>
+        <v>8000</v>
       </c>
       <c r="I20" s="3">
-        <v>464000</v>
+        <v>4000</v>
       </c>
       <c r="J20" s="3">
+        <v>49000</v>
+      </c>
+      <c r="K20" s="3">
         <v>113000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>556000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-69000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>27000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>33000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>74000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>232000</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>22624000</v>
+        <v>24987000</v>
       </c>
       <c r="E21" s="3">
-        <v>19535000</v>
+        <v>22888000</v>
       </c>
       <c r="F21" s="3">
-        <v>17380000</v>
+        <v>20630000</v>
       </c>
       <c r="G21" s="3">
-        <v>15073000</v>
+        <v>16636000</v>
       </c>
       <c r="H21" s="3">
-        <v>16073000</v>
+        <v>14884000</v>
       </c>
       <c r="I21" s="3">
-        <v>14031000</v>
+        <v>16090000</v>
       </c>
       <c r="J21" s="3">
+        <v>14168000</v>
+      </c>
+      <c r="K21" s="3">
         <v>12813000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>8941000</v>
       </c>
-      <c r="L21" s="3" t="s">
+      <c r="M21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>8159000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>7654000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2540000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>5976000</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>641000</v>
+      </c>
+      <c r="E22" s="3">
         <v>644000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>538000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>513000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>516000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>533000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>612000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>563000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>427000</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>5</v>
@@ -1315,102 +1354,111 @@
       <c r="O22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P22" s="3">
+      <c r="P22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q22" s="3">
         <v>32000</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>23916000</v>
+      </c>
+      <c r="E23" s="3">
         <v>21037000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>18136000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>16063000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>13790000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>14884000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>12806000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>11694000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>8012000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>8995000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>7724000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>7257000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2207000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>5656000</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>4173000</v>
+      </c>
+      <c r="E24" s="3">
         <v>3764000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>3179000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3752000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2924000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2804000</v>
       </c>
-      <c r="I24" s="3">
-        <v>2491000</v>
-      </c>
       <c r="J24" s="3">
+        <v>2505000</v>
+      </c>
+      <c r="K24" s="3">
         <v>4995000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2021000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2667000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2286000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2277000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>65000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2010000</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1453,99 +1501,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>19743000</v>
+      </c>
+      <c r="E26" s="3">
         <v>17273000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>14957000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>12311000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>10866000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>12080000</v>
       </c>
-      <c r="I26" s="3">
-        <v>10315000</v>
-      </c>
       <c r="J26" s="3">
+        <v>10301000</v>
+      </c>
+      <c r="K26" s="3">
         <v>6699000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>5991000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>6328000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>5438000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4980000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2142000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3646000</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>19457000</v>
+      </c>
+      <c r="E27" s="3">
         <v>16989000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>14630000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>12008000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>10475000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>11650000</v>
       </c>
-      <c r="I27" s="3">
-        <v>9956000</v>
-      </c>
       <c r="J27" s="3">
+        <v>9942000</v>
+      </c>
+      <c r="K27" s="3">
         <v>6467000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>5929000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>6313000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>5421000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4961000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2137000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3638000</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1588,32 +1645,35 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>5</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
       </c>
       <c r="H29" s="3">
         <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>-14000</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>5</v>
@@ -1630,12 +1690,15 @@
       <c r="O29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1678,9 +1741,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1723,99 +1789,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-681000</v>
+        <v>14000</v>
       </c>
       <c r="E32" s="3">
-        <v>139000</v>
+        <v>18000</v>
       </c>
       <c r="F32" s="3">
-        <v>-772000</v>
+        <v>88000</v>
       </c>
       <c r="G32" s="3">
-        <v>-225000</v>
+        <v>25000</v>
       </c>
       <c r="H32" s="3">
-        <v>-416000</v>
+        <v>-8000</v>
       </c>
       <c r="I32" s="3">
-        <v>-464000</v>
+        <v>-4000</v>
       </c>
       <c r="J32" s="3">
+        <v>-49000</v>
+      </c>
+      <c r="K32" s="3">
         <v>-113000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-556000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>69000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-27000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-33000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-74000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-232000</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>16989000</v>
+        <v>19743000</v>
       </c>
       <c r="E33" s="3">
-        <v>14630000</v>
+        <v>17273000</v>
       </c>
       <c r="F33" s="3">
-        <v>12008000</v>
+        <v>14957000</v>
       </c>
       <c r="G33" s="3">
-        <v>10475000</v>
+        <v>12311000</v>
       </c>
       <c r="H33" s="3">
-        <v>11650000</v>
+        <v>10866000</v>
       </c>
       <c r="I33" s="3">
-        <v>9942000</v>
+        <v>12080000</v>
       </c>
       <c r="J33" s="3">
+        <v>10301000</v>
+      </c>
+      <c r="K33" s="3">
         <v>6467000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>5929000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>6313000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>5421000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4961000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2137000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3638000</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1858,104 +1933,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>16989000</v>
+        <v>19743000</v>
       </c>
       <c r="E35" s="3">
-        <v>14630000</v>
+        <v>17273000</v>
       </c>
       <c r="F35" s="3">
-        <v>12008000</v>
+        <v>14957000</v>
       </c>
       <c r="G35" s="3">
-        <v>10475000</v>
+        <v>12311000</v>
       </c>
       <c r="H35" s="3">
-        <v>11650000</v>
+        <v>10866000</v>
       </c>
       <c r="I35" s="3">
-        <v>9942000</v>
+        <v>12080000</v>
       </c>
       <c r="J35" s="3">
+        <v>10301000</v>
+      </c>
+      <c r="K35" s="3">
         <v>6467000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>5929000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>6313000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>5421000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4961000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2137000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3638000</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44834</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44469</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44104</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43738</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43373</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43008</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42643</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42277</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41912</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41547</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41182</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40816</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1973,8 +2057,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1992,166 +2077,176 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>11975000</v>
+      </c>
+      <c r="E41" s="3">
         <v>16286000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>15689000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>16487000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>16289000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7838000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8162000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>9874000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5619000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3518000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1971000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2186000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2074000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2127000</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>3200000</v>
+      </c>
+      <c r="E42" s="3">
         <v>3842000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2833000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2025000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>3752000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>4236000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>3547000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>3564000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>3319000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2497000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1979000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2069000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>743000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1271000</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>4474000</v>
+        <v>7847000</v>
       </c>
       <c r="E43" s="3">
-        <v>3952000</v>
+        <v>4680000</v>
       </c>
       <c r="F43" s="3">
-        <v>3726000</v>
+        <v>4142000</v>
       </c>
       <c r="G43" s="3">
-        <v>2882000</v>
+        <v>3809000</v>
       </c>
       <c r="H43" s="3">
-        <v>4590000</v>
+        <v>2975000</v>
       </c>
       <c r="I43" s="3">
+        <v>4720000</v>
+      </c>
+      <c r="J43" s="3">
         <v>2790000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2554000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2740000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1332000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1699000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1702000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1356000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1084000</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2171,234 +2266,252 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>8930000</v>
+        <v>5557000</v>
       </c>
       <c r="E45" s="3">
-        <v>7731000</v>
+        <v>4697000</v>
       </c>
       <c r="F45" s="3">
-        <v>5369000</v>
+        <v>4367000</v>
       </c>
       <c r="G45" s="3">
-        <v>4722000</v>
+        <v>3621000</v>
       </c>
       <c r="H45" s="3">
-        <v>4306000</v>
+        <v>3071000</v>
       </c>
       <c r="I45" s="3">
-        <v>3717000</v>
+        <v>2436000</v>
       </c>
       <c r="J45" s="3">
+        <v>1742000</v>
+      </c>
+      <c r="K45" s="3">
         <v>3031000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2635000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3545000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3913000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1865000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>7613000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4708000</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>34033000</v>
+      </c>
+      <c r="E46" s="3">
         <v>33532000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>30205000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>27607000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>27645000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>20970000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>18216000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>19023000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>14313000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>10021000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>9562000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>7822000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>11786000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>9190000</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2545000</v>
+      </c>
+      <c r="E47" s="3">
         <v>1921000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2136000</v>
       </c>
-      <c r="F47" s="3">
-        <v>1705000</v>
-      </c>
       <c r="G47" s="3">
-        <v>231000</v>
+        <v>1843000</v>
       </c>
       <c r="H47" s="3">
+        <v>479000</v>
+      </c>
+      <c r="I47" s="3">
         <v>2157000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>4082000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1926000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4708000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>4056000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>3647000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>3043000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>3369000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>811000</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>3913000</v>
+        <v>2537000</v>
       </c>
       <c r="E48" s="3">
-        <v>3703000</v>
+        <v>2116000</v>
       </c>
       <c r="F48" s="3">
-        <v>3230000</v>
+        <v>2112000</v>
       </c>
       <c r="G48" s="3">
-        <v>2737000</v>
+        <v>2110000</v>
       </c>
       <c r="H48" s="3">
-        <v>2695000</v>
+        <v>2022000</v>
       </c>
       <c r="I48" s="3">
-        <v>2472000</v>
+        <v>1554000</v>
       </c>
       <c r="J48" s="3">
+        <v>1456000</v>
+      </c>
+      <c r="K48" s="3">
         <v>2253000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2150000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1888000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1892000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1732000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1634000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1541000</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>44101000</v>
+        <v>47990000</v>
       </c>
       <c r="E49" s="3">
-        <v>42852000</v>
+        <v>45898000</v>
       </c>
       <c r="F49" s="3">
-        <v>43622000</v>
+        <v>44443000</v>
       </c>
       <c r="G49" s="3">
-        <v>43718000</v>
+        <v>44742000</v>
       </c>
       <c r="H49" s="3">
-        <v>42436000</v>
+        <v>44941000</v>
       </c>
       <c r="I49" s="3">
-        <v>42752000</v>
+        <v>43577000</v>
       </c>
       <c r="J49" s="3">
+        <v>43768000</v>
+      </c>
+      <c r="K49" s="3">
         <v>42958000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>42300000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>34195000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>23164000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>23032000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>23101000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>23104000</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2441,9 +2554,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2486,54 +2602,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>7032000</v>
+        <v>7266000</v>
       </c>
       <c r="E52" s="3">
-        <v>6605000</v>
+        <v>6906000</v>
       </c>
       <c r="F52" s="3">
-        <v>6732000</v>
+        <v>6518000</v>
       </c>
       <c r="G52" s="3">
-        <v>6588000</v>
+        <v>6514000</v>
       </c>
       <c r="H52" s="3">
-        <v>4316000</v>
+        <v>5769000</v>
       </c>
       <c r="I52" s="3">
-        <v>1703000</v>
+        <v>4292000</v>
       </c>
       <c r="J52" s="3">
+        <v>1689000</v>
+      </c>
+      <c r="K52" s="3">
         <v>1817000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>564000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>216000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>304000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>327000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>123000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>114000</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2576,54 +2698,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>94511000</v>
+      </c>
+      <c r="E54" s="3">
         <v>90499000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>85501000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>82896000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>80919000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>72574000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>69225000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>67977000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>64035000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>39367000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>38569000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>35956000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>40013000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>34760000</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2641,8 +2769,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2660,79 +2789,83 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>479000</v>
+      </c>
+      <c r="E57" s="3">
         <v>375000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>340000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>266000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>174000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>156000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>183000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>179000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>203000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>127000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>147000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>184000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>152000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>169000</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="E58" s="3">
-        <v>2250000</v>
+        <v>106000</v>
       </c>
       <c r="F58" s="3">
-        <v>999000</v>
+        <v>2348000</v>
       </c>
       <c r="G58" s="3">
-        <v>2999000</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>5</v>
+        <v>1102000</v>
+      </c>
+      <c r="H58" s="3">
+        <v>3096000</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
       </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>1749000</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>5</v>
@@ -2746,132 +2879,141 @@
       <c r="O58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>22723000</v>
+        <v>20321000</v>
       </c>
       <c r="E59" s="3">
-        <v>18263000</v>
+        <v>17784000</v>
       </c>
       <c r="F59" s="3">
-        <v>14474000</v>
+        <v>13639000</v>
       </c>
       <c r="G59" s="3">
-        <v>11337000</v>
+        <v>11273000</v>
       </c>
       <c r="H59" s="3">
-        <v>13259000</v>
+        <v>8854000</v>
       </c>
       <c r="I59" s="3">
-        <v>11122000</v>
+        <v>11196000</v>
       </c>
       <c r="J59" s="3">
+        <v>9338000</v>
+      </c>
+      <c r="K59" s="3">
         <v>8066000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7843000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5309000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5859000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4151000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>7802000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3282000</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>26517000</v>
+      </c>
+      <c r="E60" s="3">
         <v>23098000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>20853000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>15739000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>14510000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>13415000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>11305000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>9994000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8046000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5355000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6006000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4335000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7954000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3451000</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>20463000</v>
+        <v>21654000</v>
       </c>
       <c r="E61" s="3">
-        <v>20200000</v>
+        <v>21189000</v>
       </c>
       <c r="F61" s="3">
-        <v>19978000</v>
+        <v>20944000</v>
       </c>
       <c r="G61" s="3">
-        <v>21071000</v>
+        <v>20449000</v>
       </c>
       <c r="H61" s="3">
+        <v>21544000</v>
+      </c>
+      <c r="I61" s="3">
         <v>16729000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>16630000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>16618000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>15882000</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -2884,54 +3026,60 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>8205000</v>
+        <v>1902000</v>
       </c>
       <c r="E62" s="3">
-        <v>8867000</v>
+        <v>2365000</v>
       </c>
       <c r="F62" s="3">
-        <v>9590000</v>
+        <v>2791000</v>
       </c>
       <c r="G62" s="3">
-        <v>9128000</v>
+        <v>2991000</v>
       </c>
       <c r="H62" s="3">
-        <v>7746000</v>
+        <v>3418000</v>
       </c>
       <c r="I62" s="3">
-        <v>7284000</v>
+        <v>2939000</v>
       </c>
       <c r="J62" s="3">
+        <v>2666000</v>
+      </c>
+      <c r="K62" s="3">
         <v>8605000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>7195000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4170000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>5150000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>4751000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>4429000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4872000</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2974,9 +3122,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3019,9 +3170,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3064,54 +3218,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>55374000</v>
+      </c>
+      <c r="E66" s="3">
         <v>51766000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>49920000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>45307000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>44709000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>37890000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>35219000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>35217000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>31123000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9525000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>11156000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>9086000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>12383000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>8323000</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3129,8 +3289,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3173,9 +3334,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3218,39 +3382,42 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>1031000</v>
+      </c>
+      <c r="E70" s="3">
         <v>1698000</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>2324000</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>3080000</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>5086000</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>5462000</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>5470000</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>5526000</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>5717000</v>
       </c>
-      <c r="L70" s="3">
-        <v>0</v>
-      </c>
       <c r="M70" s="3">
         <v>0</v>
       </c>
@@ -3263,9 +3430,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3308,54 +3478,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>17289000</v>
+      </c>
+      <c r="E72" s="3">
         <v>18040000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>16116000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>15351000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>14088000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>13502000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>11318000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>9508000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>10462000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>11843000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>9131000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>7974000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7809000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>6706000</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3398,9 +3574,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3443,9 +3622,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3488,54 +3670,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>38106000</v>
+      </c>
+      <c r="E76" s="3">
         <v>37035000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>33257000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>34509000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>31124000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>29222000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>28536000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>27234000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>27195000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>29842000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>27413000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>26870000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>27630000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>26437000</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3578,104 +3766,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44834</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44469</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44104</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43738</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43373</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43008</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42643</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42277</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41912</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41547</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41182</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40816</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>16989000</v>
+        <v>19743000</v>
       </c>
       <c r="E81" s="3">
-        <v>14630000</v>
+        <v>17273000</v>
       </c>
       <c r="F81" s="3">
-        <v>12008000</v>
+        <v>14957000</v>
       </c>
       <c r="G81" s="3">
-        <v>10475000</v>
+        <v>12311000</v>
       </c>
       <c r="H81" s="3">
-        <v>11650000</v>
+        <v>10866000</v>
       </c>
       <c r="I81" s="3">
-        <v>9942000</v>
+        <v>12080000</v>
       </c>
       <c r="J81" s="3">
+        <v>10301000</v>
+      </c>
+      <c r="K81" s="3">
         <v>6467000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>5929000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>6313000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>5421000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4961000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2137000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3638000</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3693,53 +3890,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>943000</v>
+        <v>955000</v>
       </c>
       <c r="E83" s="3">
-        <v>861000</v>
+        <v>867000</v>
       </c>
       <c r="F83" s="3">
-        <v>804000</v>
+        <v>771000</v>
       </c>
       <c r="G83" s="3">
-        <v>767000</v>
+        <v>721000</v>
       </c>
       <c r="H83" s="3">
-        <v>656000</v>
+        <v>687000</v>
       </c>
       <c r="I83" s="3">
-        <v>613000</v>
+        <v>596000</v>
       </c>
       <c r="J83" s="3">
+        <v>558000</v>
+      </c>
+      <c r="K83" s="3">
         <v>556000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>502000</v>
       </c>
-      <c r="L83" s="3" t="s">
+      <c r="M83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>435000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>397000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>333000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>288000</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3782,9 +3983,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3827,9 +4031,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3872,9 +4079,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3917,9 +4127,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3962,54 +4175,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>19950000</v>
+      </c>
+      <c r="E89" s="3">
         <v>20755000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>18849000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>15227000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>10440000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>12784000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>12941000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>9317000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>5574000</v>
-      </c>
-      <c r="L89" s="3">
-        <v>7205000</v>
       </c>
       <c r="M89" s="3">
         <v>7205000</v>
       </c>
       <c r="N89" s="3">
+        <v>7205000</v>
+      </c>
+      <c r="O89" s="3">
         <v>3022000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>5009000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3872000</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4027,53 +4246,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1257000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1059000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-970000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-705000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-736000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-756000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-718000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-707000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-523000</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-553000</v>
       </c>
       <c r="M91" s="3">
         <v>-553000</v>
       </c>
       <c r="N91" s="3">
+        <v>-553000</v>
+      </c>
+      <c r="O91" s="3">
         <v>-471000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-376000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-353000</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4116,9 +4339,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4161,54 +4387,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1926000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2006000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4288000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-152000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>1427000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-591000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3084000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>735000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-10916000</v>
       </c>
-      <c r="L94" s="3" t="s">
+      <c r="M94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-941000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1164000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2414000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2299000</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4226,53 +4458,57 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-3751000</v>
+        <v>4217000</v>
       </c>
       <c r="E96" s="3">
-        <v>-3203000</v>
+        <v>3751000</v>
       </c>
       <c r="F96" s="3">
-        <v>-2798000</v>
+        <v>3203000</v>
       </c>
       <c r="G96" s="3">
-        <v>-2664000</v>
+        <v>2798000</v>
       </c>
       <c r="H96" s="3">
-        <v>-2269000</v>
+        <v>2664000</v>
       </c>
       <c r="I96" s="3">
-        <v>-1918000</v>
+        <v>2269000</v>
       </c>
       <c r="J96" s="3">
+        <v>1918000</v>
+      </c>
+      <c r="K96" s="3">
         <v>-1579000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-1350000</v>
-      </c>
-      <c r="L96" s="3">
-        <v>-1006000</v>
       </c>
       <c r="M96" s="3">
         <v>-1006000</v>
       </c>
       <c r="N96" s="3">
+        <v>-1006000</v>
+      </c>
+      <c r="O96" s="3">
         <v>-864000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-595000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-423000</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4315,9 +4551,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4360,9 +4599,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4405,142 +4647,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-20633000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-17772000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-12696000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-14410000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-3968000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-12061000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-10790000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-5924000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>7477000</v>
       </c>
-      <c r="L100" s="3" t="s">
+      <c r="M100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-6478000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1746000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2655000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-3304000</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>382000</v>
+      </c>
+      <c r="E101" s="3">
         <v>636000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1287000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-37000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>440000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-277000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-101000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>236000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-34000</v>
       </c>
-      <c r="L101" s="3" t="s">
+      <c r="M101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1000</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
       <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
         <v>7000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2227000</v>
+      </c>
+      <c r="E102" s="3">
         <v>1613000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>578000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>628000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>8339000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-145000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1034000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>4364000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2101000</v>
-      </c>
-      <c r="L102" s="3">
-        <v>-215000</v>
       </c>
       <c r="M102" s="3">
         <v>-215000</v>
       </c>
       <c r="N102" s="3">
+        <v>-215000</v>
+      </c>
+      <c r="O102" s="3">
         <v>112000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-53000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1740000</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
